--- a/Cloud_Expert_Data.xlsx
+++ b/Cloud_Expert_Data.xlsx
@@ -232,25 +232,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>32.0</v>
+        <v>53.0</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>12.0</v>
+        <v>28.0</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>0.375</v>
+        <v>0.5283018867924528</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>440.0</v>
+        <v>487.0</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>210.0</v>
+        <v>237.0</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.486652977412731</v>
       </c>
       <c r="L2" s="4" t="n">
-        <v>-0.10227272727272728</v>
+        <v>0.04164890937972182</v>
       </c>
     </row>
     <row r="3">
@@ -266,17 +266,17 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
         <is>
-          <t>杨育明</t>
+          <t>叶诗程</t>
         </is>
       </c>
       <c r="F3" s="6" t="n">
@@ -289,16 +289,16 @@
         <v>1.0</v>
       </c>
       <c r="I3" s="6" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="J3" s="6" t="n">
-        <v>6.0</v>
+        <v>4.0</v>
       </c>
       <c r="K3" s="7" t="n">
-        <v>0.5454545454545454</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="L3" s="7" t="n">
-        <v>0.4545454545454546</v>
+        <v>0.4285714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -314,17 +314,17 @@
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>29244</t>
+          <t>40269</t>
         </is>
       </c>
       <c r="E4" s="8" t="inlineStr">
         <is>
-          <t>陈鸿</t>
+          <t>何凤英</t>
         </is>
       </c>
       <c r="F4" s="9" t="n">
@@ -335,13 +335,13 @@
       </c>
       <c r="H4" s="10"/>
       <c r="I4" s="9" t="n">
-        <v>6.0</v>
+        <v>11.0</v>
       </c>
       <c r="J4" s="9" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K4" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.2727272727272727</v>
       </c>
       <c r="L4" s="10"/>
     </row>
@@ -358,17 +358,17 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>34825</t>
+          <t>68026</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
-          <t>陈琪琪</t>
+          <t>王莹</t>
         </is>
       </c>
       <c r="F5" s="6" t="n">
@@ -379,13 +379,13 @@
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="6" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="J5" s="6" t="n">
-        <v>4.0</v>
+        <v>7.0</v>
       </c>
       <c r="K5" s="7" t="n">
-        <v>0.8</v>
+        <v>0.7</v>
       </c>
       <c r="L5" s="12"/>
     </row>
@@ -402,17 +402,17 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr">
         <is>
-          <t>41262</t>
+          <t>76474</t>
         </is>
       </c>
       <c r="E6" s="8" t="inlineStr">
         <is>
-          <t>陈彬</t>
+          <t>陈明华</t>
         </is>
       </c>
       <c r="F6" s="9" t="n">
@@ -423,13 +423,13 @@
       </c>
       <c r="H6" s="10"/>
       <c r="I6" s="9" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="J6" s="9" t="n">
-        <v>6.0</v>
+        <v>3.0</v>
       </c>
       <c r="K6" s="11" t="n">
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
       <c r="L6" s="10"/>
     </row>
@@ -446,17 +446,17 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>68930</t>
+          <t>82308</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
-          <t>梁晓鹏</t>
+          <t>郑元辉</t>
         </is>
       </c>
       <c r="F7" s="6" t="n">
@@ -470,10 +470,10 @@
         <v>2.0</v>
       </c>
       <c r="J7" s="6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K7" s="7" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L7" s="12"/>
     </row>
@@ -490,17 +490,17 @@
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>厦门湖里翔远路</t>
+          <t>厦门集美岩兴路</t>
         </is>
       </c>
       <c r="D8" s="8" t="inlineStr">
         <is>
-          <t>75295</t>
+          <t>85137</t>
         </is>
       </c>
       <c r="E8" s="8" t="inlineStr">
         <is>
-          <t>吴泉水</t>
+          <t>姜盛昕</t>
         </is>
       </c>
       <c r="F8" s="9" t="n">
@@ -511,195 +511,195 @@
       </c>
       <c r="H8" s="10"/>
       <c r="I8" s="9" t="n">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="J8" s="9" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="K8" s="11" t="n">
-        <v>0.6</v>
+        <v>0.0</v>
       </c>
       <c r="L8" s="10"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>厦门湖里翔远路</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>77540</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>祝本山</t>
-        </is>
-      </c>
-      <c r="F9" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G9" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H9" s="12"/>
-      <c r="I9" s="6" t="n">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>泉州洛江</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>74775</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>王光辉</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K9" s="11" t="n">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="L9" s="11" t="n">
+        <v>0.8571428571428572</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>泉州洛江</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>7062</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="inlineStr">
+        <is>
+          <t>曾晓明</t>
+        </is>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H10" s="12"/>
+      <c r="I10" s="6" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="J10" s="6" t="n">
         <v>4.0</v>
       </c>
-      <c r="J9" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="K9" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L9" s="12"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>厦门湖里翔远路</t>
-        </is>
-      </c>
-      <c r="D10" s="8" t="inlineStr">
-        <is>
-          <t>84712</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>罗志滨</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G10" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H10" s="10"/>
-      <c r="I10" s="9" t="n">
+      <c r="K10" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L10" s="12"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>泉州洛江</t>
+        </is>
+      </c>
+      <c r="D11" s="8" t="inlineStr">
+        <is>
+          <t>71998</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>朱嘉民</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G11" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9" t="n">
         <v>4.0</v>
       </c>
-      <c r="J10" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K10" s="11" t="n">
+      <c r="J11" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K11" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L10" s="10"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>厦门湖里翔远路</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>9728</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>苏飞鹏</t>
-        </is>
-      </c>
-      <c r="F11" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H11" s="12"/>
-      <c r="I11" s="6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K11" s="7" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="L11" s="12"/>
+      <c r="L11" s="10"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
-        <is>
-          <t>莆田城厢万达</t>
-        </is>
-      </c>
-      <c r="D12" s="8" t="inlineStr">
-        <is>
-          <t>74513</t>
-        </is>
-      </c>
-      <c r="E12" s="8" t="inlineStr">
-        <is>
-          <t>曾黛媚</t>
-        </is>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G12" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I12" s="9" t="n">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>泉州洛江</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>85192</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>谢誉</t>
+        </is>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="12"/>
+      <c r="I12" s="6" t="n">
         <v>6.0</v>
       </c>
-      <c r="J12" s="9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="K12" s="11" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>0.16666666666666663</v>
-      </c>
+      <c r="J12" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="L12" s="12"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -714,17 +714,17 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>福州万象城</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>85808</t>
+          <t>70951</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>王东</t>
+          <t>陈海沣</t>
         </is>
       </c>
       <c r="F13" s="6" t="n">
@@ -737,16 +737,16 @@
         <v>1.0</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>3.0</v>
       </c>
       <c r="K13" s="7" t="n">
-        <v>0.6</v>
+        <v>1.0</v>
       </c>
       <c r="L13" s="7" t="n">
-        <v>0.4</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="14">
@@ -762,17 +762,17 @@
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>福州万象城</t>
         </is>
       </c>
       <c r="D14" s="8" t="inlineStr">
         <is>
-          <t>56006</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="E14" s="8" t="inlineStr">
         <is>
-          <t>朱海亮</t>
+          <t>曾颖慧</t>
         </is>
       </c>
       <c r="F14" s="9" t="n">
@@ -783,13 +783,13 @@
       </c>
       <c r="H14" s="10"/>
       <c r="I14" s="9" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="J14" s="9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K14" s="11" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="L14" s="10"/>
     </row>
@@ -806,17 +806,17 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>福州万象城</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>75446</t>
+          <t>42000</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
-          <t>张姝昕</t>
+          <t>游燕云</t>
         </is>
       </c>
       <c r="F15" s="6" t="n">
@@ -827,13 +827,13 @@
       </c>
       <c r="H15" s="12"/>
       <c r="I15" s="6" t="n">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="J15" s="6" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K15" s="7" t="n">
-        <v>0.5</v>
+        <v>1.0</v>
       </c>
       <c r="L15" s="12"/>
     </row>
@@ -850,36 +850,40 @@
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>莆田城厢万达</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D16" s="8" t="inlineStr">
         <is>
-          <t>80612</t>
+          <t>13316</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
         <is>
-          <t>林璐瑶</t>
+          <t>薛楚娴</t>
         </is>
       </c>
       <c r="F16" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G16" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H16" s="10"/>
+        <v>1.0</v>
+      </c>
+      <c r="H16" s="11" t="n">
+        <v>1.0</v>
+      </c>
       <c r="I16" s="9" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="J16" s="9" t="n">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K16" s="11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L16" s="10"/>
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="L16" s="11" t="n">
+        <v>0.2857142857142857</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -894,17 +898,17 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>68026</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
-          <t>王莹</t>
+          <t>郑宇豪</t>
         </is>
       </c>
       <c r="F17" s="6" t="n">
@@ -917,16 +921,16 @@
         <v>1.0</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>10.0</v>
+        <v>6.0</v>
       </c>
       <c r="J17" s="6" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="K17" s="7" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="L17" s="7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="18">
@@ -942,39 +946,39 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D18" s="8" t="inlineStr">
         <is>
-          <t>76474</t>
+          <t>79416</t>
         </is>
       </c>
       <c r="E18" s="8" t="inlineStr">
         <is>
-          <t>陈明华</t>
+          <t>黄坚</t>
         </is>
       </c>
       <c r="F18" s="9" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G18" s="9" t="n">
         <v>1.0</v>
       </c>
       <c r="H18" s="11" t="n">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="I18" s="9" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="J18" s="9" t="n">
         <v>4.0</v>
       </c>
-      <c r="J18" s="9" t="n">
-        <v>3.0</v>
-      </c>
       <c r="K18" s="11" t="n">
-        <v>0.75</v>
+        <v>0.4</v>
       </c>
       <c r="L18" s="11" t="n">
-        <v>0.25</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="19">
@@ -990,40 +994,36 @@
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>82308</t>
+          <t>71343</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
         <is>
-          <t>郑元辉</t>
+          <t>陈浩</t>
         </is>
       </c>
       <c r="F19" s="6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H19" s="7" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="H19" s="12"/>
       <c r="I19" s="6" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="J19" s="6" t="n">
         <v>2.0</v>
       </c>
       <c r="K19" s="7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L19" s="7" t="n">
-        <v>0.0</v>
-      </c>
+        <v>0.4</v>
+      </c>
+      <c r="L19" s="12"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
@@ -1038,40 +1038,36 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>福州榕泰</t>
         </is>
       </c>
       <c r="D20" s="8" t="inlineStr">
         <is>
-          <t>40269</t>
+          <t>79388</t>
         </is>
       </c>
       <c r="E20" s="8" t="inlineStr">
         <is>
-          <t>何凤英</t>
+          <t>池政霖</t>
         </is>
       </c>
       <c r="F20" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G20" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="H20" s="11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="H20" s="10"/>
       <c r="I20" s="9" t="n">
-        <v>11.0</v>
+        <v>7.0</v>
       </c>
       <c r="J20" s="9" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="K20" s="11" t="n">
-        <v>0.2727272727272727</v>
-      </c>
-      <c r="L20" s="11" t="n">
-        <v>-0.2727272727272727</v>
-      </c>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="L20" s="10"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -1086,36 +1082,40 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>龙岩新罗物流大道</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>11765</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>叶诗程</t>
+          <t>滕小龙</t>
         </is>
       </c>
       <c r="F21" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H21" s="12"/>
+        <v>1.0</v>
+      </c>
+      <c r="H21" s="7" t="n">
+        <v>1.0</v>
+      </c>
       <c r="I21" s="6" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="J21" s="6" t="n">
         <v>6.0</v>
       </c>
-      <c r="J21" s="6" t="n">
-        <v>3.0</v>
-      </c>
       <c r="K21" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L21" s="12"/>
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="L21" s="7" t="n">
+        <v>0.33333333333333337</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
@@ -1130,308 +1130,320 @@
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>厦门集美岩兴路</t>
+          <t>龙岩新罗物流大道</t>
         </is>
       </c>
       <c r="D22" s="8" t="inlineStr">
         <is>
-          <t>85137</t>
+          <t>9232</t>
         </is>
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>姜盛昕</t>
+          <t>刘斌</t>
         </is>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G22" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H22" s="10"/>
+        <v>1.0</v>
+      </c>
+      <c r="H22" s="11" t="n">
+        <v>1.0</v>
+      </c>
       <c r="I22" s="9" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J22" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="K22" s="11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L22" s="10"/>
+        <v>0.5</v>
+      </c>
+      <c r="L22" s="11" t="n">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C23" s="8" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D23" s="8" t="inlineStr">
-        <is>
-          <t>71761</t>
-        </is>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>朱静榕</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G23" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="H23" s="11" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="I23" s="9" t="n">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>龙岩新罗物流大道</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>80164</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>简政文</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I23" s="6" t="n">
         <v>6.0</v>
       </c>
-      <c r="J23" s="9" t="n">
+      <c r="J23" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K23" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L23" s="7" t="n">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C24" s="8" t="inlineStr">
+        <is>
+          <t>龙岩新罗物流大道</t>
+        </is>
+      </c>
+      <c r="D24" s="8" t="inlineStr">
+        <is>
+          <t>18869</t>
+        </is>
+      </c>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>林倩茹</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G24" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H24" s="10"/>
+      <c r="I24" s="9" t="n">
         <v>5.0</v>
       </c>
-      <c r="K23" s="11" t="n">
-        <v>0.8333333333333333</v>
-      </c>
-      <c r="L23" s="11" t="n">
-        <v>0.16666666666666663</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>79905</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>钟榕涛</t>
-        </is>
-      </c>
-      <c r="F24" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H24" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K24" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L24" s="7" t="n">
-        <v>-0.2</v>
-      </c>
+      <c r="J24" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K24" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L24" s="10"/>
     </row>
     <row r="25">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B25" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C25" s="8" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D25" s="8" t="inlineStr">
-        <is>
-          <t>33106</t>
-        </is>
-      </c>
-      <c r="E25" s="8" t="inlineStr">
-        <is>
-          <t>黄莹</t>
-        </is>
-      </c>
-      <c r="F25" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G25" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H25" s="10"/>
-      <c r="I25" s="9" t="n">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>龙岩新罗物流大道</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>72624</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>廖裕森</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="J25" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K25" s="7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="L25" s="12"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="inlineStr">
+        <is>
+          <t>泉州鲤城</t>
+        </is>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>19147</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>郑铭</t>
+        </is>
+      </c>
+      <c r="F26" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G26" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H26" s="11" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I26" s="9" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="J26" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K26" s="11" t="n">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="L26" s="11" t="n">
+        <v>0.5714285714285714</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>泉州鲤城</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>82845</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>田丹丹</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="G27" s="6" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I27" s="6" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="J27" s="6" t="n">
         <v>4.0</v>
       </c>
-      <c r="J25" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K25" s="11" t="n">
+      <c r="K27" s="7" t="n">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="L27" s="7" t="n">
+        <v>0.7333333333333334</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="inlineStr">
+        <is>
+          <t>泉州鲤城</t>
+        </is>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>34870</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>李柠</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G28" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H28" s="11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I28" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="J28" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K28" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L25" s="10"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>51085</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>黎金城</t>
-        </is>
-      </c>
-      <c r="F26" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H26" s="12"/>
-      <c r="I26" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J26" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K26" s="7" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L26" s="12"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C27" s="8" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D27" s="8" t="inlineStr">
-        <is>
-          <t>70412</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>易连建</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J27" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K27" s="11" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L27" s="10"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>福州东二环泰禾</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>77833</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>李瀚</t>
-        </is>
-      </c>
-      <c r="F28" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H28" s="12"/>
-      <c r="I28" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J28" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K28" s="7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="L28" s="12"/>
+      <c r="L28" s="11" t="n">
+        <v>-0.5</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -1451,34 +1463,34 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>19147</t>
+          <t>81434</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>郑铭</t>
+          <t>黄育玲</t>
         </is>
       </c>
       <c r="F29" s="6" t="n">
         <v>1.0</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I29" s="6" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="J29" s="6" t="n">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K29" s="7" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.0</v>
       </c>
       <c r="L29" s="7" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="30">
@@ -1508,14 +1520,12 @@
         </is>
       </c>
       <c r="F30" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G30" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="H30" s="11" t="n">
-        <v>1.0</v>
-      </c>
+        <v>0.0</v>
+      </c>
+      <c r="H30" s="10"/>
       <c r="I30" s="9" t="n">
         <v>7.0</v>
       </c>
@@ -1525,9 +1535,7 @@
       <c r="K30" s="11" t="n">
         <v>0.7142857142857143</v>
       </c>
-      <c r="L30" s="11" t="n">
-        <v>0.2857142857142857</v>
-      </c>
+      <c r="L30" s="10"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -1542,39 +1550,39 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>泉州鲤城</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>82845</t>
+          <t>29244</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>田丹丹</t>
+          <t>陈鸿</t>
         </is>
       </c>
       <c r="F31" s="6" t="n">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="G31" s="6" t="n">
         <v>1.0</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.33333333333333326</v>
+        <v>1.0</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>13.0</v>
+        <v>7.0</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K31" s="7" t="n">
-        <v>0.15384615384615385</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="L31" s="7" t="n">
-        <v>0.17948717948717946</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="32">
@@ -1590,39 +1598,39 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>泉州鲤城</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D32" s="8" t="inlineStr">
         <is>
-          <t>34870</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>李柠</t>
+          <t>杨育明</t>
         </is>
       </c>
       <c r="F32" s="9" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G32" s="9" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="H32" s="11" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="I32" s="9" t="n">
-        <v>2.0</v>
+        <v>13.0</v>
       </c>
       <c r="J32" s="9" t="n">
-        <v>1.0</v>
+        <v>8.0</v>
       </c>
       <c r="K32" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6153846153846154</v>
       </c>
       <c r="L32" s="11" t="n">
-        <v>-0.5</v>
+        <v>0.3846153846153846</v>
       </c>
     </row>
     <row r="33">
@@ -1638,36 +1646,40 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>泉州鲤城</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>81434</t>
+          <t>9728</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>黄育玲</t>
+          <t>苏飞鹏</t>
         </is>
       </c>
       <c r="F33" s="6" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H33" s="12"/>
+        <v>1.0</v>
+      </c>
+      <c r="H33" s="7" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I33" s="6" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
       <c r="J33" s="6" t="n">
-        <v>0.0</v>
+        <v>3.0</v>
       </c>
       <c r="K33" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L33" s="12"/>
+        <v>0.6</v>
+      </c>
+      <c r="L33" s="7" t="n">
+        <v>-0.1</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
@@ -1682,39 +1694,39 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D34" s="8" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>41262</t>
         </is>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
-          <t>戴丽容</t>
+          <t>陈彬</t>
         </is>
       </c>
       <c r="F34" s="9" t="n">
         <v>1.0</v>
       </c>
       <c r="G34" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="H34" s="11" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="I34" s="9" t="n">
-        <v>4.0</v>
+        <v>8.0</v>
       </c>
       <c r="J34" s="9" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="K34" s="11" t="n">
         <v>0.75</v>
       </c>
       <c r="L34" s="11" t="n">
-        <v>0.25</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="35">
@@ -1730,17 +1742,17 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>19070</t>
+          <t>75295</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>林伟坤</t>
+          <t>吴泉水</t>
         </is>
       </c>
       <c r="F35" s="6" t="n">
@@ -1753,16 +1765,16 @@
         <v>0.0</v>
       </c>
       <c r="I35" s="6" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
       <c r="J35" s="6" t="n">
         <v>3.0</v>
       </c>
       <c r="K35" s="7" t="n">
-        <v>0.3</v>
+        <v>0.42857142857142855</v>
       </c>
       <c r="L35" s="7" t="n">
-        <v>-0.3</v>
+        <v>-0.42857142857142855</v>
       </c>
     </row>
     <row r="36">
@@ -1778,40 +1790,36 @@
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D36" s="8" t="inlineStr">
         <is>
-          <t>69819</t>
+          <t>34825</t>
         </is>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
-          <t>朱晓生</t>
+          <t>陈琪琪</t>
         </is>
       </c>
       <c r="F36" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G36" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="H36" s="11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="H36" s="10"/>
       <c r="I36" s="9" t="n">
         <v>5.0</v>
       </c>
       <c r="J36" s="9" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="K36" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L36" s="11" t="n">
-        <v>-0.4</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="L36" s="10"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -1826,40 +1834,36 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>79527</t>
+          <t>68930</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>陈艺惠</t>
+          <t>梁晓鹏</t>
         </is>
       </c>
       <c r="F37" s="6" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G37" s="6" t="n">
         <v>0.0</v>
       </c>
-      <c r="H37" s="7" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="H37" s="12"/>
       <c r="I37" s="6" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="J37" s="6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K37" s="7" t="n">
         <v>0.5</v>
       </c>
-      <c r="L37" s="7" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="L37" s="12"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
@@ -1874,17 +1878,17 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>14321</t>
+          <t>77540</t>
         </is>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
-          <t>林敏</t>
+          <t>祝本山</t>
         </is>
       </c>
       <c r="F38" s="9" t="n">
@@ -1895,13 +1899,13 @@
       </c>
       <c r="H38" s="10"/>
       <c r="I38" s="9" t="n">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="J38" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="K38" s="11" t="n">
-        <v>0.5</v>
+        <v>0.0</v>
       </c>
       <c r="L38" s="10"/>
     </row>
@@ -1918,17 +1922,17 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>漳州龙文北路</t>
+          <t>厦门湖里翔远路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>19255</t>
+          <t>84712</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>林艺超</t>
+          <t>罗志滨</t>
         </is>
       </c>
       <c r="F39" s="6" t="n">
@@ -1967,31 +1971,35 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>41067</t>
+          <t>19255</t>
         </is>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
-          <t>刘祎明</t>
+          <t>林艺超</t>
         </is>
       </c>
       <c r="F40" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G40" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H40" s="10"/>
+        <v>1.0</v>
+      </c>
+      <c r="H40" s="11" t="n">
+        <v>1.0</v>
+      </c>
       <c r="I40" s="9" t="n">
-        <v>9.0</v>
+        <v>5.0</v>
       </c>
       <c r="J40" s="9" t="n">
         <v>3.0</v>
       </c>
       <c r="K40" s="11" t="n">
-        <v>0.33333333333333326</v>
-      </c>
-      <c r="L40" s="10"/>
+        <v>0.6</v>
+      </c>
+      <c r="L40" s="11" t="n">
+        <v>0.4</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -2011,31 +2019,35 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>72729</t>
+          <t>41067</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>陈鸿浩</t>
+          <t>刘祎明</t>
         </is>
       </c>
       <c r="F41" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H41" s="12"/>
+        <v>1.0</v>
+      </c>
+      <c r="H41" s="7" t="n">
+        <v>1.0</v>
+      </c>
       <c r="I41" s="6" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
       <c r="J41" s="6" t="n">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="K41" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="L41" s="12"/>
+        <v>0.4</v>
+      </c>
+      <c r="L41" s="7" t="n">
+        <v>0.6</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="8" t="inlineStr">
@@ -2055,31 +2067,35 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>74146</t>
+          <t>69819</t>
         </is>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
-          <t>张淑玲</t>
+          <t>朱晓生</t>
         </is>
       </c>
       <c r="F42" s="9" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="G42" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H42" s="10"/>
+        <v>1.0</v>
+      </c>
+      <c r="H42" s="11" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I42" s="9" t="n">
-        <v>2.0</v>
+        <v>7.0</v>
       </c>
       <c r="J42" s="9" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="K42" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L42" s="10"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="L42" s="11" t="n">
+        <v>0.07142857142857145</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
@@ -2094,39 +2110,39 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>33878</t>
+          <t>72729</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
         <is>
-          <t>张亚兰</t>
+          <t>陈鸿浩</t>
         </is>
       </c>
       <c r="F43" s="6" t="n">
         <v>2.0</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="I43" s="6" t="n">
         <v>4.0</v>
       </c>
       <c r="J43" s="6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K43" s="7" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L43" s="7" t="n">
-        <v>-0.5</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="44">
@@ -2142,21 +2158,21 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>80313</t>
+          <t>14321</t>
         </is>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>卢健</t>
+          <t>林敏</t>
         </is>
       </c>
       <c r="F44" s="9" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G44" s="9" t="n">
         <v>0.0</v>
@@ -2165,16 +2181,16 @@
         <v>0.0</v>
       </c>
       <c r="I44" s="9" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="J44" s="9" t="n">
         <v>1.0</v>
       </c>
       <c r="K44" s="11" t="n">
-        <v>0.2</v>
+        <v>0.25</v>
       </c>
       <c r="L44" s="11" t="n">
-        <v>-0.2</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="45">
@@ -2190,17 +2206,17 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>74790</t>
+          <t>19070</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>陈萌田</t>
+          <t>林伟坤</t>
         </is>
       </c>
       <c r="F45" s="6" t="n">
@@ -2211,13 +2227,13 @@
       </c>
       <c r="H45" s="12"/>
       <c r="I45" s="6" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="J45" s="6" t="n">
         <v>3.0</v>
       </c>
-      <c r="J45" s="6" t="n">
-        <v>2.0</v>
-      </c>
       <c r="K45" s="7" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="L45" s="12"/>
     </row>
@@ -2234,17 +2250,17 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>76221</t>
+          <t>32925</t>
         </is>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>柯智鹏</t>
+          <t>戴丽容</t>
         </is>
       </c>
       <c r="F46" s="9" t="n">
@@ -2255,13 +2271,13 @@
       </c>
       <c r="H46" s="10"/>
       <c r="I46" s="9" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="J46" s="9" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K46" s="11" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="L46" s="10"/>
     </row>
@@ -2278,17 +2294,17 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>87018</t>
+          <t>74146</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
         <is>
-          <t>李秀惠</t>
+          <t>张淑玲</t>
         </is>
       </c>
       <c r="F47" s="6" t="n">
@@ -2299,13 +2315,13 @@
       </c>
       <c r="H47" s="12"/>
       <c r="I47" s="6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J47" s="6" t="n">
         <v>1.0</v>
       </c>
       <c r="K47" s="7" t="n">
-        <v>1.0</v>
+        <v>0.5</v>
       </c>
       <c r="L47" s="12"/>
     </row>
@@ -2322,17 +2338,17 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>厦门海沧马青路</t>
+          <t>漳州龙文北路</t>
         </is>
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>87242</t>
+          <t>79527</t>
         </is>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
-          <t>陈山</t>
+          <t>陈艺惠</t>
         </is>
       </c>
       <c r="F48" s="9" t="n">
@@ -2343,371 +2359,383 @@
       </c>
       <c r="H48" s="10"/>
       <c r="I48" s="9" t="n">
-        <v>7.0</v>
+        <v>4.0</v>
       </c>
       <c r="J48" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K48" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L48" s="10"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>45425</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>陈维锟</t>
+        </is>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="I49" s="6" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="J49" s="6" t="n">
         <v>5.0</v>
       </c>
-      <c r="K48" s="11" t="n">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="L48" s="10"/>
-    </row>
-    <row r="49">
-      <c r="A49" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B49" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="K49" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L49" s="7" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>79381</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>吴丽琴</t>
+        </is>
+      </c>
+      <c r="F50" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G50" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H50" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I50" s="9" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="J50" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="K50" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="L50" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>87554</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>郑韵秋</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H51" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I51" s="6" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="J51" s="6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="K51" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L51" s="7" t="n">
+        <v>-0.5</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B52" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C52" s="8" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D52" s="8" t="inlineStr">
+        <is>
+          <t>39053</t>
+        </is>
+      </c>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>李规发</t>
+        </is>
+      </c>
+      <c r="F52" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G52" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H52" s="10"/>
+      <c r="I52" s="9" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="J52" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K52" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L52" s="10"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr">
+        <is>
+          <t>75824</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>林义明</t>
+        </is>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H53" s="12"/>
+      <c r="I53" s="6" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="K53" s="7" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="L53" s="12"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B54" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D54" s="8" t="inlineStr">
+        <is>
+          <t>85882</t>
+        </is>
+      </c>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>翁佳美</t>
+        </is>
+      </c>
+      <c r="F54" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G54" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H54" s="10"/>
+      <c r="I54" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="J54" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K54" s="11" t="n">
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="L54" s="10"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>福州仓山金林路</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr">
+        <is>
+          <t>88234</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>刘敏</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G55" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H55" s="12"/>
+      <c r="I55" s="6" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="J55" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K55" s="7" t="n">
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="L55" s="12"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B56" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C56" s="8" t="inlineStr">
         <is>
           <t>泉州晋江</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
-        <is>
-          <t>45637</t>
-        </is>
-      </c>
-      <c r="E49" s="8" t="inlineStr">
-        <is>
-          <t>郭佳</t>
-        </is>
-      </c>
-      <c r="F49" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G49" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H49" s="11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I49" s="9" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J49" s="9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K49" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L49" s="11" t="n">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>53000</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>朱晓恩</t>
-        </is>
-      </c>
-      <c r="F50" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H50" s="12"/>
-      <c r="I50" s="6" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="J50" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K50" s="7" t="n">
-        <v>0.33333333333333326</v>
-      </c>
-      <c r="L50" s="12"/>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C51" s="8" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D51" s="8" t="inlineStr">
-        <is>
-          <t>59551</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>洪志远</t>
-        </is>
-      </c>
-      <c r="F51" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G51" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H51" s="10"/>
-      <c r="I51" s="9" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="J51" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K51" s="11" t="n">
-        <v>0.16666666666666663</v>
-      </c>
-      <c r="L51" s="10"/>
-    </row>
-    <row r="52">
-      <c r="A52" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>60185</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>倪彬灿</t>
-        </is>
-      </c>
-      <c r="F52" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H52" s="12"/>
-      <c r="I52" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="J52" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K52" s="7" t="n">
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>74891</t>
+        </is>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>康桃芳</t>
+        </is>
+      </c>
+      <c r="F56" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G56" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H56" s="11" t="n">
         <v>0.5</v>
       </c>
-      <c r="L52" s="12"/>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C53" s="8" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D53" s="8" t="inlineStr">
-        <is>
-          <t>62528</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr">
-        <is>
-          <t>何飞飞</t>
-        </is>
-      </c>
-      <c r="F53" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G53" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H53" s="10"/>
-      <c r="I53" s="9" t="n">
+      <c r="I56" s="9" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="J56" s="9" t="n">
         <v>4.0</v>
       </c>
-      <c r="J53" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K53" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L53" s="10"/>
-    </row>
-    <row r="54">
-      <c r="A54" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B54" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C54" s="5" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D54" s="5" t="inlineStr">
-        <is>
-          <t>74891</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="inlineStr">
-        <is>
-          <t>康桃芳</t>
-        </is>
-      </c>
-      <c r="F54" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G54" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H54" s="12"/>
-      <c r="I54" s="6" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="J54" s="6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K54" s="7" t="n">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="L54" s="12"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B55" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D55" s="8" t="inlineStr">
-        <is>
-          <t>75518</t>
-        </is>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>周培鑫</t>
-        </is>
-      </c>
-      <c r="F55" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G55" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H55" s="10"/>
-      <c r="I55" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="J55" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K55" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L55" s="10"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>泉州晋江</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>76274</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>冯密密</t>
-        </is>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H56" s="12"/>
-      <c r="I56" s="6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="J56" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K56" s="7" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L56" s="12"/>
+      <c r="K56" s="11" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="L56" s="11" t="n">
+        <v>0.05555555555555558</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
@@ -2722,39 +2750,39 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>74775</t>
+          <t>76274</t>
         </is>
       </c>
       <c r="E57" s="5" t="inlineStr">
         <is>
-          <t>王光辉</t>
+          <t>冯密密</t>
         </is>
       </c>
       <c r="F57" s="6" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="G57" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H57" s="7" t="n">
-        <v>0.0</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="I57" s="6" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J57" s="6" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K57" s="7" t="n">
-        <v>0.0</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L57" s="7" t="n">
-        <v>0.0</v>
+        <v>0.047619047619047616</v>
       </c>
     </row>
     <row r="58">
@@ -2770,17 +2798,17 @@
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D58" s="8" t="inlineStr">
         <is>
-          <t>7062</t>
+          <t>45637</t>
         </is>
       </c>
       <c r="E58" s="8" t="inlineStr">
         <is>
-          <t>曾晓明</t>
+          <t>郭佳</t>
         </is>
       </c>
       <c r="F58" s="9" t="n">
@@ -2791,13 +2819,13 @@
       </c>
       <c r="H58" s="10"/>
       <c r="I58" s="9" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="J58" s="9" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="K58" s="11" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="L58" s="10"/>
     </row>
@@ -2814,17 +2842,17 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>71998</t>
+          <t>53000</t>
         </is>
       </c>
       <c r="E59" s="5" t="inlineStr">
         <is>
-          <t>朱嘉民</t>
+          <t>朱晓恩</t>
         </is>
       </c>
       <c r="F59" s="6" t="n">
@@ -2835,13 +2863,13 @@
       </c>
       <c r="H59" s="12"/>
       <c r="I59" s="6" t="n">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="J59" s="6" t="n">
         <v>2.0</v>
       </c>
       <c r="K59" s="7" t="n">
-        <v>0.5</v>
+        <v>0.33333333333333326</v>
       </c>
       <c r="L59" s="12"/>
     </row>
@@ -2858,17 +2886,17 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>泉州洛江</t>
+          <t>泉州晋江</t>
         </is>
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>85192</t>
+          <t>59551</t>
         </is>
       </c>
       <c r="E60" s="8" t="inlineStr">
         <is>
-          <t>谢誉</t>
+          <t>洪志远</t>
         </is>
       </c>
       <c r="F60" s="9" t="n">
@@ -2882,148 +2910,144 @@
         <v>6.0</v>
       </c>
       <c r="J60" s="9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K60" s="11" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.16666666666666663</v>
       </c>
       <c r="L60" s="10"/>
     </row>
     <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B61" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C61" s="8" t="inlineStr">
-        <is>
-          <t>福州万象城</t>
-        </is>
-      </c>
-      <c r="D61" s="8" t="inlineStr">
-        <is>
-          <t>19526</t>
-        </is>
-      </c>
-      <c r="E61" s="8" t="inlineStr">
-        <is>
-          <t>曾颖慧</t>
-        </is>
-      </c>
-      <c r="F61" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="G61" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H61" s="11" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I61" s="9" t="n">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>泉州晋江</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr">
+        <is>
+          <t>60185</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>倪彬灿</t>
+        </is>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G61" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H61" s="12"/>
+      <c r="I61" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="J61" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K61" s="7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L61" s="12"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B62" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C62" s="8" t="inlineStr">
+        <is>
+          <t>泉州晋江</t>
+        </is>
+      </c>
+      <c r="D62" s="8" t="inlineStr">
+        <is>
+          <t>62528</t>
+        </is>
+      </c>
+      <c r="E62" s="8" t="inlineStr">
+        <is>
+          <t>何飞飞</t>
+        </is>
+      </c>
+      <c r="F62" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G62" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H62" s="10"/>
+      <c r="I62" s="9" t="n">
         <v>4.0</v>
       </c>
-      <c r="J61" s="9" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="K61" s="11" t="n">
+      <c r="J62" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K62" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="L61" s="11" t="n">
-        <v>-0.25</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B62" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C62" s="5" t="inlineStr">
-        <is>
-          <t>福州万象城</t>
-        </is>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>42000</t>
-        </is>
-      </c>
-      <c r="E62" s="5" t="inlineStr">
-        <is>
-          <t>游燕云</t>
-        </is>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G62" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H62" s="12"/>
-      <c r="I62" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="J62" s="6" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="K62" s="7" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L62" s="12"/>
+      <c r="L62" s="10"/>
     </row>
     <row r="63">
-      <c r="A63" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B63" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C63" s="8" t="inlineStr">
-        <is>
-          <t>福州万象城</t>
-        </is>
-      </c>
-      <c r="D63" s="8" t="inlineStr">
-        <is>
-          <t>70951</t>
-        </is>
-      </c>
-      <c r="E63" s="8" t="inlineStr">
-        <is>
-          <t>陈海沣</t>
-        </is>
-      </c>
-      <c r="F63" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G63" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H63" s="10"/>
-      <c r="I63" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="J63" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K63" s="11" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="L63" s="10"/>
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>泉州晋江</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>75518</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>周培鑫</t>
+        </is>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G63" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H63" s="12"/>
+      <c r="I63" s="6" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="J63" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K63" s="7" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="L63" s="12"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -3038,39 +3062,39 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>31798</t>
+          <t>74399</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>陈欣莹</t>
+          <t>林健明</t>
         </is>
       </c>
       <c r="F64" s="6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="G64" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="H64" s="7" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="I64" s="6" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="J64" s="6" t="n">
         <v>5.0</v>
       </c>
-      <c r="J64" s="6" t="n">
-        <v>1.0</v>
-      </c>
       <c r="K64" s="7" t="n">
-        <v>0.2</v>
+        <v>0.625</v>
       </c>
       <c r="L64" s="7" t="n">
-        <v>-0.2</v>
+        <v>-0.125</v>
       </c>
     </row>
     <row r="65">
@@ -3086,36 +3110,40 @@
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D65" s="8" t="inlineStr">
         <is>
-          <t>71318</t>
+          <t>38468</t>
         </is>
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>谭祺</t>
+          <t>谢鹭飞</t>
         </is>
       </c>
       <c r="F65" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G65" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="H65" s="10"/>
+      <c r="H65" s="11" t="n">
+        <v>0.0</v>
+      </c>
       <c r="I65" s="9" t="n">
         <v>3.0</v>
       </c>
       <c r="J65" s="9" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K65" s="11" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="L65" s="10"/>
+        <v>0.33333333333333326</v>
+      </c>
+      <c r="L65" s="11" t="n">
+        <v>-0.33333333333333326</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
@@ -3130,17 +3158,17 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>75600</t>
+          <t>59808</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>周凡翔</t>
+          <t>林静静</t>
         </is>
       </c>
       <c r="F66" s="6" t="n">
@@ -3174,17 +3202,17 @@
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D67" s="8" t="inlineStr">
         <is>
-          <t>76116</t>
+          <t>70597</t>
         </is>
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>陈嘉琦</t>
+          <t>林星星</t>
         </is>
       </c>
       <c r="F67" s="9" t="n">
@@ -3195,13 +3223,13 @@
       </c>
       <c r="H67" s="10"/>
       <c r="I67" s="9" t="n">
-        <v>5.0</v>
+        <v>10.0</v>
       </c>
       <c r="J67" s="9" t="n">
-        <v>0.0</v>
+        <v>7.0</v>
       </c>
       <c r="K67" s="11" t="n">
-        <v>0.0</v>
+        <v>0.7</v>
       </c>
       <c r="L67" s="10"/>
     </row>
@@ -3218,17 +3246,17 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>福州仓山万达</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>81440</t>
+          <t>72901</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>董维娜</t>
+          <t>黄世伟</t>
         </is>
       </c>
       <c r="F68" s="6" t="n">
@@ -3239,13 +3267,13 @@
       </c>
       <c r="H68" s="12"/>
       <c r="I68" s="6" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="J68" s="6" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="K68" s="7" t="n">
-        <v>1.0</v>
+        <v>0.6</v>
       </c>
       <c r="L68" s="12"/>
     </row>
@@ -3262,312 +3290,308 @@
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>福州榕泰</t>
+          <t>厦门宝龙一城</t>
         </is>
       </c>
       <c r="D69" s="8" t="inlineStr">
         <is>
-          <t>13316</t>
+          <t>87674</t>
         </is>
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>薛楚娴</t>
+          <t>李宇豪</t>
         </is>
       </c>
       <c r="F69" s="9" t="n">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G69" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="H69" s="11" t="n">
-        <v>0.0</v>
-      </c>
+      <c r="H69" s="10"/>
       <c r="I69" s="9" t="n">
-        <v>7.0</v>
+        <v>3.0</v>
       </c>
       <c r="J69" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K69" s="11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="L69" s="10"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B70" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C70" s="8" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D70" s="8" t="inlineStr">
+        <is>
+          <t>71761</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
+        <is>
+          <t>朱静榕</t>
+        </is>
+      </c>
+      <c r="F70" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="G70" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="H70" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I70" s="9" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="J70" s="9" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="K70" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="L70" s="11" t="n">
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B71" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D71" s="5" t="inlineStr">
+        <is>
+          <t>77833</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="inlineStr">
+        <is>
+          <t>李瀚</t>
+        </is>
+      </c>
+      <c r="F71" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G71" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H71" s="7" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I71" s="6" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K71" s="7" t="n">
+        <v>0.16666666666666663</v>
+      </c>
+      <c r="L71" s="7" t="n">
+        <v>-0.16666666666666663</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B72" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C72" s="8" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>33106</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
+        <is>
+          <t>黄莹</t>
+        </is>
+      </c>
+      <c r="F72" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G72" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H72" s="10"/>
+      <c r="I72" s="9" t="n">
         <v>4.0</v>
       </c>
-      <c r="K69" s="11" t="n">
-        <v>0.5714285714285714</v>
-      </c>
-      <c r="L69" s="11" t="n">
-        <v>-0.5714285714285714</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B70" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C70" s="5" t="inlineStr">
-        <is>
-          <t>福州榕泰</t>
-        </is>
-      </c>
-      <c r="D70" s="5" t="inlineStr">
-        <is>
-          <t>71343</t>
-        </is>
-      </c>
-      <c r="E70" s="5" t="inlineStr">
-        <is>
-          <t>陈浩</t>
-        </is>
-      </c>
-      <c r="F70" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G70" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H70" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I70" s="6" t="n">
+      <c r="J72" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K72" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L72" s="10"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B73" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D73" s="5" t="inlineStr">
+        <is>
+          <t>51085</t>
+        </is>
+      </c>
+      <c r="E73" s="5" t="inlineStr">
+        <is>
+          <t>黎金城</t>
+        </is>
+      </c>
+      <c r="F73" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G73" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H73" s="12"/>
+      <c r="I73" s="6" t="n">
         <v>5.0</v>
       </c>
-      <c r="J70" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K70" s="7" t="n">
+      <c r="J73" s="6" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K73" s="7" t="n">
         <v>0.4</v>
       </c>
-      <c r="L70" s="7" t="n">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B71" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C71" s="8" t="inlineStr">
-        <is>
-          <t>福州榕泰</t>
-        </is>
-      </c>
-      <c r="D71" s="8" t="inlineStr">
-        <is>
-          <t>29685</t>
-        </is>
-      </c>
-      <c r="E71" s="8" t="inlineStr">
-        <is>
-          <t>郑宇豪</t>
-        </is>
-      </c>
-      <c r="F71" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G71" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H71" s="10"/>
-      <c r="I71" s="9" t="n">
+      <c r="L73" s="12"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C74" s="8" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D74" s="8" t="inlineStr">
+        <is>
+          <t>70412</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>易连建</t>
+        </is>
+      </c>
+      <c r="F74" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G74" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H74" s="10"/>
+      <c r="I74" s="9" t="n">
         <v>5.0</v>
       </c>
-      <c r="J71" s="9" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K71" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="L71" s="10"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B72" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C72" s="5" t="inlineStr">
-        <is>
-          <t>福州榕泰</t>
-        </is>
-      </c>
-      <c r="D72" s="5" t="inlineStr">
-        <is>
-          <t>79388</t>
-        </is>
-      </c>
-      <c r="E72" s="5" t="inlineStr">
-        <is>
-          <t>池政霖</t>
-        </is>
-      </c>
-      <c r="F72" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G72" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H72" s="12"/>
-      <c r="I72" s="6" t="n">
-        <v>7.0</v>
-      </c>
-      <c r="J72" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K72" s="7" t="n">
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="L72" s="12"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B73" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C73" s="8" t="inlineStr">
-        <is>
-          <t>福州榕泰</t>
-        </is>
-      </c>
-      <c r="D73" s="8" t="inlineStr">
-        <is>
-          <t>79416</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>黄坚</t>
-        </is>
-      </c>
-      <c r="F73" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G73" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H73" s="10"/>
-      <c r="I73" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="J73" s="9" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="K73" s="11" t="n">
-        <v>0.375</v>
-      </c>
-      <c r="L73" s="10"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B74" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C74" s="5" t="inlineStr">
-        <is>
-          <t>龙岩新罗物流大道</t>
-        </is>
-      </c>
-      <c r="D74" s="5" t="inlineStr">
-        <is>
-          <t>80164</t>
-        </is>
-      </c>
-      <c r="E74" s="5" t="inlineStr">
-        <is>
-          <t>简政文</t>
-        </is>
-      </c>
-      <c r="F74" s="6" t="n">
-        <v>1.0</v>
-      </c>
-      <c r="G74" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H74" s="7" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="I74" s="6" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="J74" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K74" s="7" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L74" s="7" t="n">
-        <v>-0.5</v>
-      </c>
+      <c r="J74" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K74" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L74" s="10"/>
     </row>
     <row r="75">
-      <c r="A75" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B75" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C75" s="8" t="inlineStr">
-        <is>
-          <t>龙岩新罗物流大道</t>
-        </is>
-      </c>
-      <c r="D75" s="8" t="inlineStr">
-        <is>
-          <t>11765</t>
-        </is>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>滕小龙</t>
-        </is>
-      </c>
-      <c r="F75" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G75" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H75" s="10"/>
-      <c r="I75" s="9" t="n">
-        <v>8.0</v>
-      </c>
-      <c r="J75" s="9" t="n">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B75" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C75" s="5" t="inlineStr">
+        <is>
+          <t>福州东二环泰禾</t>
+        </is>
+      </c>
+      <c r="D75" s="5" t="inlineStr">
+        <is>
+          <t>79905</t>
+        </is>
+      </c>
+      <c r="E75" s="5" t="inlineStr">
+        <is>
+          <t>钟榕涛</t>
+        </is>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G75" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H75" s="12"/>
+      <c r="I75" s="6" t="n">
         <v>5.0</v>
       </c>
-      <c r="K75" s="11" t="n">
-        <v>0.625</v>
-      </c>
-      <c r="L75" s="10"/>
+      <c r="J75" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K75" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L75" s="12"/>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
@@ -3582,36 +3606,40 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>龙岩新罗物流大道</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>18869</t>
+          <t>33878</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>林倩茹</t>
+          <t>张亚兰</t>
         </is>
       </c>
       <c r="F76" s="6" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G76" s="6" t="n">
         <v>0.0</v>
       </c>
-      <c r="H76" s="12"/>
+      <c r="H76" s="7" t="n">
+        <v>0.0</v>
+      </c>
       <c r="I76" s="6" t="n">
         <v>5.0</v>
       </c>
       <c r="J76" s="6" t="n">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="K76" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L76" s="12"/>
+        <v>0.4</v>
+      </c>
+      <c r="L76" s="7" t="n">
+        <v>-0.4</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
@@ -3626,36 +3654,40 @@
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>龙岩新罗物流大道</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr">
         <is>
-          <t>72624</t>
+          <t>87242</t>
         </is>
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>廖裕森</t>
+          <t>陈山</t>
         </is>
       </c>
       <c r="F77" s="9" t="n">
-        <v>0.0</v>
+        <v>1.0</v>
       </c>
       <c r="G77" s="9" t="n">
         <v>0.0</v>
       </c>
-      <c r="H77" s="10"/>
+      <c r="H77" s="11" t="n">
+        <v>0.0</v>
+      </c>
       <c r="I77" s="9" t="n">
-        <v>3.0</v>
+        <v>8.0</v>
       </c>
       <c r="J77" s="9" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K77" s="11" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="L77" s="10"/>
+        <v>0.625</v>
+      </c>
+      <c r="L77" s="11" t="n">
+        <v>-0.625</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
@@ -3670,17 +3702,17 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>龙岩新罗物流大道</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>9232</t>
+          <t>74790</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>刘斌</t>
+          <t>陈萌田</t>
         </is>
       </c>
       <c r="F78" s="6" t="n">
@@ -3691,13 +3723,13 @@
       </c>
       <c r="H78" s="12"/>
       <c r="I78" s="6" t="n">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="J78" s="6" t="n">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
       <c r="K78" s="7" t="n">
-        <v>0.0</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="L78" s="12"/>
     </row>
@@ -3714,17 +3746,17 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>厦门宝龙一城</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D79" s="8" t="inlineStr">
         <is>
-          <t>38468</t>
+          <t>76221</t>
         </is>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>谢鹭飞</t>
+          <t>柯智鹏</t>
         </is>
       </c>
       <c r="F79" s="9" t="n">
@@ -3735,13 +3767,13 @@
       </c>
       <c r="H79" s="10"/>
       <c r="I79" s="9" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="J79" s="9" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="K79" s="11" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
       <c r="L79" s="10"/>
     </row>
@@ -3758,17 +3790,17 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>厦门宝龙一城</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>59808</t>
+          <t>80313</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>林静静</t>
+          <t>卢健</t>
         </is>
       </c>
       <c r="F80" s="6" t="n">
@@ -3779,13 +3811,13 @@
       </c>
       <c r="H80" s="12"/>
       <c r="I80" s="6" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J80" s="6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="K80" s="7" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.25</v>
       </c>
       <c r="L80" s="12"/>
     </row>
@@ -3802,17 +3834,17 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>厦门宝龙一城</t>
+          <t>厦门海沧马青路</t>
         </is>
       </c>
       <c r="D81" s="8" t="inlineStr">
         <is>
-          <t>70597</t>
+          <t>87018</t>
         </is>
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>林星星</t>
+          <t>李秀惠</t>
         </is>
       </c>
       <c r="F81" s="9" t="n">
@@ -3823,147 +3855,151 @@
       </c>
       <c r="H81" s="10"/>
       <c r="I81" s="9" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
       <c r="J81" s="9" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
       <c r="K81" s="11" t="n">
-        <v>0.7</v>
+        <v>1.0</v>
       </c>
       <c r="L81" s="10"/>
     </row>
     <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B82" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C82" s="5" t="inlineStr">
-        <is>
-          <t>厦门宝龙一城</t>
-        </is>
-      </c>
-      <c r="D82" s="5" t="inlineStr">
-        <is>
-          <t>72901</t>
-        </is>
-      </c>
-      <c r="E82" s="5" t="inlineStr">
-        <is>
-          <t>黄世伟</t>
-        </is>
-      </c>
-      <c r="F82" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G82" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H82" s="12"/>
-      <c r="I82" s="6" t="n">
+      <c r="A82" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B82" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C82" s="8" t="inlineStr">
+        <is>
+          <t>福州仓山万达</t>
+        </is>
+      </c>
+      <c r="D82" s="8" t="inlineStr">
+        <is>
+          <t>81440</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>董维娜</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="G82" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H82" s="11" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="I82" s="9" t="n">
+        <v>3.0</v>
+      </c>
+      <c r="J82" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K82" s="11" t="n">
+        <v>0.6666666666666665</v>
+      </c>
+      <c r="L82" s="11" t="n">
+        <v>-0.6666666666666665</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>福州仓山万达</t>
+        </is>
+      </c>
+      <c r="D83" s="5" t="inlineStr">
+        <is>
+          <t>31798</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>陈欣莹</t>
+        </is>
+      </c>
+      <c r="F83" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G83" s="6" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H83" s="12"/>
+      <c r="I83" s="6" t="n">
         <v>5.0</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="J83" s="6" t="n">
+        <v>1.0</v>
+      </c>
+      <c r="K83" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L83" s="12"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>福建战区</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>福建一部</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>福州仓山万达</t>
+        </is>
+      </c>
+      <c r="D84" s="8" t="inlineStr">
+        <is>
+          <t>71318</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>谭祺</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="G84" s="9" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="H84" s="10"/>
+      <c r="I84" s="9" t="n">
         <v>3.0</v>
       </c>
-      <c r="K82" s="7" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="L82" s="12"/>
-    </row>
-    <row r="83">
-      <c r="A83" s="8" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B83" s="8" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C83" s="8" t="inlineStr">
-        <is>
-          <t>厦门宝龙一城</t>
-        </is>
-      </c>
-      <c r="D83" s="8" t="inlineStr">
-        <is>
-          <t>74399</t>
-        </is>
-      </c>
-      <c r="E83" s="8" t="inlineStr">
-        <is>
-          <t>林健明</t>
-        </is>
-      </c>
-      <c r="F83" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G83" s="9" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H83" s="10"/>
-      <c r="I83" s="9" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="J83" s="9" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="K83" s="11" t="n">
+      <c r="J84" s="9" t="n">
+        <v>2.0</v>
+      </c>
+      <c r="K84" s="11" t="n">
         <v>0.6666666666666665</v>
       </c>
-      <c r="L83" s="10"/>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>福建战区</t>
-        </is>
-      </c>
-      <c r="B84" s="5" t="inlineStr">
-        <is>
-          <t>福建一部</t>
-        </is>
-      </c>
-      <c r="C84" s="5" t="inlineStr">
-        <is>
-          <t>厦门宝龙一城</t>
-        </is>
-      </c>
-      <c r="D84" s="5" t="inlineStr">
-        <is>
-          <t>87674</t>
-        </is>
-      </c>
-      <c r="E84" s="5" t="inlineStr">
-        <is>
-          <t>李宇豪</t>
-        </is>
-      </c>
-      <c r="F84" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="G84" s="6" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="H84" s="12"/>
-      <c r="I84" s="6" t="n">
-        <v>3.0</v>
-      </c>
-      <c r="J84" s="6" t="n">
-        <v>2.0</v>
-      </c>
-      <c r="K84" s="7" t="n">
-        <v>0.6666666666666665</v>
-      </c>
-      <c r="L84" s="12"/>
+      <c r="L84" s="10"/>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
@@ -3978,17 +4014,17 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>福州仓山万达</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>39053</t>
+          <t>75600</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>李规发</t>
+          <t>周凡翔</t>
         </is>
       </c>
       <c r="F85" s="6" t="n">
@@ -3999,13 +4035,13 @@
       </c>
       <c r="H85" s="12"/>
       <c r="I85" s="6" t="n">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="J85" s="6" t="n">
         <v>2.0</v>
       </c>
       <c r="K85" s="7" t="n">
-        <v>0.5</v>
+        <v>0.6666666666666665</v>
       </c>
       <c r="L85" s="12"/>
     </row>
@@ -4022,17 +4058,17 @@
       </c>
       <c r="C86" s="8" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>福州仓山万达</t>
         </is>
       </c>
       <c r="D86" s="8" t="inlineStr">
         <is>
-          <t>45425</t>
+          <t>76116</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
         <is>
-          <t>陈维锟</t>
+          <t>陈嘉琦</t>
         </is>
       </c>
       <c r="F86" s="9" t="n">
@@ -4043,13 +4079,13 @@
       </c>
       <c r="H86" s="10"/>
       <c r="I86" s="9" t="n">
-        <v>8.0</v>
+        <v>5.0</v>
       </c>
       <c r="J86" s="9" t="n">
-        <v>3.0</v>
+        <v>0.0</v>
       </c>
       <c r="K86" s="11" t="n">
-        <v>0.375</v>
+        <v>0.0</v>
       </c>
       <c r="L86" s="10"/>
     </row>
@@ -4066,17 +4102,17 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>75824</t>
+          <t>56006</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>林义明</t>
+          <t>朱海亮</t>
         </is>
       </c>
       <c r="F87" s="6" t="n">
@@ -4087,13 +4123,13 @@
       </c>
       <c r="H87" s="12"/>
       <c r="I87" s="6" t="n">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="J87" s="6" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="K87" s="7" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L87" s="12"/>
     </row>
@@ -4110,17 +4146,17 @@
       </c>
       <c r="C88" s="8" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D88" s="8" t="inlineStr">
         <is>
-          <t>79381</t>
+          <t>74513</t>
         </is>
       </c>
       <c r="E88" s="8" t="inlineStr">
         <is>
-          <t>吴丽琴</t>
+          <t>曾黛媚</t>
         </is>
       </c>
       <c r="F88" s="9" t="n">
@@ -4131,13 +4167,13 @@
       </c>
       <c r="H88" s="10"/>
       <c r="I88" s="9" t="n">
-        <v>3.0</v>
+        <v>6.0</v>
       </c>
       <c r="J88" s="9" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K88" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.8333333333333333</v>
       </c>
       <c r="L88" s="10"/>
     </row>
@@ -4154,17 +4190,17 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>85882</t>
+          <t>75446</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>翁佳美</t>
+          <t>张姝昕</t>
         </is>
       </c>
       <c r="F89" s="6" t="n">
@@ -4175,13 +4211,13 @@
       </c>
       <c r="H89" s="12"/>
       <c r="I89" s="6" t="n">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="J89" s="6" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K89" s="7" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.5</v>
       </c>
       <c r="L89" s="12"/>
     </row>
@@ -4198,17 +4234,17 @@
       </c>
       <c r="C90" s="8" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D90" s="8" t="inlineStr">
         <is>
-          <t>87554</t>
+          <t>80612</t>
         </is>
       </c>
       <c r="E90" s="8" t="inlineStr">
         <is>
-          <t>郑韵秋</t>
+          <t>林璐瑶</t>
         </is>
       </c>
       <c r="F90" s="9" t="n">
@@ -4219,13 +4255,13 @@
       </c>
       <c r="H90" s="10"/>
       <c r="I90" s="9" t="n">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="J90" s="9" t="n">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="K90" s="11" t="n">
-        <v>0.6666666666666665</v>
+        <v>0.0</v>
       </c>
       <c r="L90" s="10"/>
     </row>
@@ -4242,17 +4278,17 @@
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>福州仓山金林路</t>
+          <t>莆田城厢万达</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>85808</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>刘敏</t>
+          <t>王东</t>
         </is>
       </c>
       <c r="F91" s="6" t="n">
@@ -4263,13 +4299,13 @@
       </c>
       <c r="H91" s="12"/>
       <c r="I91" s="6" t="n">
-        <v>6.0</v>
+        <v>5.0</v>
       </c>
       <c r="J91" s="6" t="n">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="K91" s="7" t="n">
-        <v>0.33333333333333326</v>
+        <v>0.6</v>
       </c>
       <c r="L91" s="12"/>
     </row>
